--- a/塗り絵/リスト一覧.xlsx
+++ b/塗り絵/リスト一覧.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業\塗り絵\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\副業\塗り絵\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8070B1B-6876-41AD-A1FE-E892D9AA86F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D03D6C-2B16-42DA-B1D3-50F1CAAC98A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{85BDEC4A-5A8D-44F3-A2DC-E2A9DAF3FECA}"/>
+    <workbookView xWindow="1170" yWindow="1380" windowWidth="16700" windowHeight="7760" xr2:uid="{85BDEC4A-5A8D-44F3-A2DC-E2A9DAF3FECA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>リスト</t>
     <phoneticPr fontId="1"/>
@@ -274,6 +272,19 @@
   </si>
   <si>
     <t>ブーケ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>着物の女の子</t>
+    <rPh sb="0" eb="2">
+      <t>キモノ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オンナ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>コ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -713,16 +724,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38A01A1E-D309-40E1-950C-AD95B7FAE085}">
   <dimension ref="B2:G30"/>
-  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="6.25" customWidth="1"/>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="80.6875" customWidth="1"/>
+    <col min="4" max="4" width="80.6640625" customWidth="1"/>
     <col min="5" max="7" width="6.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
@@ -742,7 +753,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="2">
         <v>1</v>
       </c>
@@ -756,7 +767,7 @@
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
     </row>
-    <row r="4" spans="2:7" ht="52.9" x14ac:dyDescent="0.7">
+    <row r="4" spans="2:7" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="2">
         <v>2</v>
       </c>
@@ -770,7 +781,7 @@
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="2">
         <v>3</v>
       </c>
@@ -781,10 +792,12 @@
       <c r="E5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="4"/>
+      <c r="F5" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="2">
         <v>4</v>
       </c>
@@ -796,7 +809,7 @@
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="2">
         <v>5</v>
       </c>
@@ -808,7 +821,7 @@
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="2">
         <v>6</v>
       </c>
@@ -820,7 +833,7 @@
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="2">
         <v>7</v>
       </c>
@@ -832,7 +845,7 @@
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="2">
         <v>8</v>
       </c>
@@ -844,7 +857,7 @@
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="2">
         <v>9</v>
       </c>
@@ -856,7 +869,7 @@
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="2">
         <v>10</v>
       </c>
@@ -868,7 +881,7 @@
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="2">
         <v>11</v>
       </c>
@@ -882,7 +895,7 @@
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="2">
         <v>12</v>
       </c>
@@ -894,7 +907,7 @@
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="2">
         <v>13</v>
       </c>
@@ -906,7 +919,7 @@
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="2">
         <v>14</v>
       </c>
@@ -918,7 +931,7 @@
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="2">
         <v>15</v>
       </c>
@@ -930,7 +943,7 @@
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="2">
         <v>16</v>
       </c>
@@ -942,7 +955,7 @@
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="2">
         <v>17</v>
       </c>
@@ -954,7 +967,7 @@
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="2">
         <v>18</v>
       </c>
@@ -966,17 +979,19 @@
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="2">
         <v>19</v>
       </c>
-      <c r="C21" s="2"/>
+      <c r="C21" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="D21" s="2"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="2">
         <v>20</v>
       </c>
@@ -986,7 +1001,7 @@
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="2">
         <v>21</v>
       </c>
@@ -996,7 +1011,7 @@
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" s="2">
         <v>22</v>
       </c>
@@ -1006,7 +1021,7 @@
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="2">
         <v>23</v>
       </c>
@@ -1016,7 +1031,7 @@
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="2">
         <v>24</v>
       </c>
@@ -1026,7 +1041,7 @@
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" s="2">
         <v>25</v>
       </c>
@@ -1036,7 +1051,7 @@
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="2">
         <v>26</v>
       </c>
@@ -1046,7 +1061,7 @@
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="2">
         <v>27</v>
       </c>
@@ -1056,7 +1071,7 @@
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.7">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" s="2">
         <v>28</v>
       </c>

--- a/塗り絵/リスト一覧.xlsx
+++ b/塗り絵/リスト一覧.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\副業\塗り絵\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chie\１８.副業\塗り絵\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D03D6C-2B16-42DA-B1D3-50F1CAAC98A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{832D0739-4C1D-49EA-8436-E17940AB0B1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1380" windowWidth="16700" windowHeight="7760" xr2:uid="{85BDEC4A-5A8D-44F3-A2DC-E2A9DAF3FECA}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{85BDEC4A-5A8D-44F3-A2DC-E2A9DAF3FECA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>リスト</t>
     <phoneticPr fontId="1"/>
@@ -285,6 +285,10 @@
     <rPh sb="5" eb="6">
       <t>コ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザート</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -724,16 +728,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38A01A1E-D309-40E1-950C-AD95B7FAE085}">
   <dimension ref="B2:G30"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="6.25" customWidth="1"/>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="80.6640625" customWidth="1"/>
+    <col min="4" max="4" width="80.6875" customWidth="1"/>
     <col min="5" max="7" width="6.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
@@ -753,7 +757,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B3" s="2">
         <v>1</v>
       </c>
@@ -767,7 +771,7 @@
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
     </row>
-    <row r="4" spans="2:7" ht="54" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:7" ht="52.9" x14ac:dyDescent="0.7">
       <c r="B4" s="2">
         <v>2</v>
       </c>
@@ -781,7 +785,7 @@
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B5" s="2">
         <v>3</v>
       </c>
@@ -797,7 +801,7 @@
       </c>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B6" s="2">
         <v>4</v>
       </c>
@@ -809,7 +813,7 @@
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B7" s="2">
         <v>5</v>
       </c>
@@ -821,7 +825,7 @@
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B8" s="2">
         <v>6</v>
       </c>
@@ -833,7 +837,7 @@
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B9" s="2">
         <v>7</v>
       </c>
@@ -845,7 +849,7 @@
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B10" s="2">
         <v>8</v>
       </c>
@@ -857,7 +861,7 @@
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B11" s="2">
         <v>9</v>
       </c>
@@ -869,7 +873,7 @@
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B12" s="2">
         <v>10</v>
       </c>
@@ -881,7 +885,7 @@
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B13" s="2">
         <v>11</v>
       </c>
@@ -895,7 +899,7 @@
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B14" s="2">
         <v>12</v>
       </c>
@@ -907,7 +911,7 @@
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B15" s="2">
         <v>13</v>
       </c>
@@ -919,7 +923,7 @@
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B16" s="2">
         <v>14</v>
       </c>
@@ -931,7 +935,7 @@
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B17" s="2">
         <v>15</v>
       </c>
@@ -943,7 +947,7 @@
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B18" s="2">
         <v>16</v>
       </c>
@@ -955,7 +959,7 @@
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B19" s="2">
         <v>17</v>
       </c>
@@ -967,7 +971,7 @@
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B20" s="2">
         <v>18</v>
       </c>
@@ -979,7 +983,7 @@
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B21" s="2">
         <v>19</v>
       </c>
@@ -991,17 +995,19 @@
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B22" s="2">
         <v>20</v>
       </c>
-      <c r="C22" s="2"/>
+      <c r="C22" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="D22" s="2"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B23" s="2">
         <v>21</v>
       </c>
@@ -1011,7 +1017,7 @@
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B24" s="2">
         <v>22</v>
       </c>
@@ -1021,7 +1027,7 @@
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B25" s="2">
         <v>23</v>
       </c>
@@ -1031,7 +1037,7 @@
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B26" s="2">
         <v>24</v>
       </c>
@@ -1041,7 +1047,7 @@
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B27" s="2">
         <v>25</v>
       </c>
@@ -1051,7 +1057,7 @@
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B28" s="2">
         <v>26</v>
       </c>
@@ -1061,7 +1067,7 @@
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B29" s="2">
         <v>27</v>
       </c>
@@ -1071,7 +1077,7 @@
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.7">
       <c r="B30" s="2">
         <v>28</v>
       </c>
